--- a/data/trans_orig/P2C_R1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1887</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1855</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189940</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191827</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>187961</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>189773</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>379745</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>381600</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297448</t>
+          <t>297611</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>399887</t>
+          <t>399952</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>703303</t>
+          <t>702411</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713985</t>
+          <t>713549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24599</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>497836</t>
+          <t>497419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>509457</t>
+          <t>508628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>571208</t>
+          <t>571552</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>585210</t>
+          <t>584741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1075223</t>
+          <t>1076628</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1092219</t>
+          <t>1093138</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>285055</t>
+          <t>285290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>228844</t>
+          <t>227117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>516726</t>
+          <t>517769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>527179</t>
+          <t>527183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,97 +2105,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1228</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1919</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6175</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1228</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6999</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6123</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1228</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>6130</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106183</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108102</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193380</t>
+          <t>194204</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302351</t>
+          <t>302358</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285795</t>
+          <t>284305</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336787</t>
+          <t>336636</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>626289</t>
+          <t>626167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>633577</t>
+          <t>633583</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205585</t>
+          <t>205390</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>328775</t>
+          <t>327426</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>537373</t>
+          <t>536940</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>28173</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>41428</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1889549</t>
+          <t>1890151</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1905490</t>
+          <t>1904747</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2271632</t>
+          <t>2273189</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2290698</t>
+          <t>2291168</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4166825</t>
+          <t>4170160</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4192098</t>
+          <t>4192924</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,97 +3712,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1946</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1944</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>174534</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176480</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>214846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216790</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>391318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>393269</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4055,62 +4055,62 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7648</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3598</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7685</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11504</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3598</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12545</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15666</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312847</t>
+          <t>312884</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>320532</t>
+          <t>319596</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,49 +4183,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>421198</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>413292</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>424796</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>421198</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>412251</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>424796</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>702</t>
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729662</t>
+          <t>729271</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743391</t>
+          <t>743409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18278</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15687</t>
+          <t>15785</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>26734</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>551277</t>
+          <t>552969</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>566664</t>
+          <t>566751</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>594078</t>
+          <t>593980</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>606767</t>
+          <t>606747</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1151419</t>
+          <t>1152587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1170600</t>
+          <t>1170861</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>14987</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366646</t>
+          <t>366745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>374215</t>
+          <t>374207</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>297013</t>
+          <t>296915</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>306614</t>
+          <t>306620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667884</t>
+          <t>667903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>679684</t>
+          <t>679739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>14288</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139705</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141764</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207566</t>
+          <t>208320</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>219144</t>
+          <t>220038</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>349689</t>
+          <t>349594</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>360974</t>
+          <t>360902</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>976</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>298765</t>
+          <t>298823</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>345013</t>
+          <t>344286</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>647674</t>
+          <t>647663</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>654923</t>
+          <t>654921</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242800</t>
+          <t>242089</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>373704</t>
+          <t>373694</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>383585</t>
+          <t>383614</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>618558</t>
+          <t>620241</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>631294</t>
+          <t>631349</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>28419</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18997</t>
+          <t>18056</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41757</t>
+          <t>41584</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32174</t>
+          <t>31692</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61541</t>
+          <t>61375</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2110561</t>
+          <t>2108907</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2127869</t>
+          <t>2127599</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2475073</t>
+          <t>2475246</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2497833</t>
+          <t>2498774</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4592615</t>
+          <t>4592781</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4621982</t>
+          <t>4622464</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,97 +6691,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1886</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152668</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154729</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>173063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174949</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>327707</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>329678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,62 +7069,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5083</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>6085</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>254896</t>
+          <t>255371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356523</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>613005</t>
+          <t>614007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>11508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17594</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>23600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>453107</t>
+          <t>452868</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462768</t>
+          <t>463314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>523615</t>
+          <t>524326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>536723</t>
+          <t>537289</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>982826</t>
+          <t>981984</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>998064</t>
+          <t>998488</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>14125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>20177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325199</t>
+          <t>325833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336733</t>
+          <t>336861</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>306168</t>
+          <t>306100</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>314784</t>
+          <t>314770</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>635789</t>
+          <t>635637</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>649449</t>
+          <t>649538</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>958</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122726</t>
+          <t>123530</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199731</t>
+          <t>199530</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>326381</t>
+          <t>325723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>333848</t>
+          <t>333857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,77 +8426,77 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>4174</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10381</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>5126</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>11367</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4174</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1027</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>9506</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>5126</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>11480</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>295352</t>
+          <t>295802</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -8534,82 +8534,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>342025</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>335818</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>345116</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>98,79%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>641701</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>635460</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>644858</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>98,24%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>342025</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>336693</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>345172</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>97,25%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>641701</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>635347</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>644769</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10458</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>240676</t>
+          <t>240056</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>383375</t>
+          <t>382333</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>392586</t>
+          <t>392577</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>626938</t>
+          <t>627290</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>638088</t>
+          <t>638086</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27109</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>33490</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29413</t>
+          <t>28035</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54728</t>
+          <t>54523</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1869819</t>
+          <t>1869753</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1886325</t>
+          <t>1886093</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2299130</t>
+          <t>2301530</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2320607</t>
+          <t>2320099</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4177220</t>
+          <t>4177425</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4202535</t>
+          <t>4203913</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12930</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24607</t>
+          <t>24615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42910</t>
+          <t>42305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56293</t>
+          <t>56235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35487</t>
+          <t>38806</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>94720</t>
+          <t>94757</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130863</t>
+          <t>134594</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110234</t>
+          <t>109960</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129891</t>
+          <t>129752</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242086</t>
+          <t>242838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251125</t>
+          <t>251302</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18714</t>
+          <t>18377</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>13921</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11767</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28375</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84877</t>
+          <t>85214</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98383</t>
+          <t>98577</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97278</t>
+          <t>97352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106453</t>
+          <t>106562</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>186489</t>
+          <t>187322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>203097</t>
+          <t>203297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>18326</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12611</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>26764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45147</t>
+          <t>45489</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56895</t>
+          <t>56914</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57687</t>
+          <t>57537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65490</t>
+          <t>65753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106673</t>
+          <t>106485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120638</t>
+          <t>120870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70633</t>
+          <t>71579</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78435</t>
+          <t>79921</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>28267</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36750</t>
+          <t>36429</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>198740</t>
+          <t>197794</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>265687</t>
+          <t>265829</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>233334</t>
+          <t>231848</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>306085</t>
+          <t>305804</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32707</t>
+          <t>32766</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46471</t>
+          <t>46789</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>75586</t>
+          <t>76361</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>95661</t>
+          <t>95339</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>114165</t>
+          <t>113274</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137978</t>
+          <t>137770</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37485</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51249</t>
+          <t>51190</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>88254</t>
+          <t>88576</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>108329</t>
+          <t>107554</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>129892</t>
+          <t>130100</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>153705</t>
+          <t>154596</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,71%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66947</t>
+          <t>66767</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97983</t>
+          <t>99445</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57911</t>
+          <t>64709</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>162248</t>
+          <t>162854</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>120183</t>
+          <t>118878</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>245408</t>
+          <t>245815</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>391270</t>
+          <t>389808</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>422306</t>
+          <t>422486</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>734586</t>
+          <t>733980</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>838923</t>
+          <t>832125</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1140679</t>
+          <t>1140272</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1265904</t>
+          <t>1267209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Edad-trans_orig.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297611</t>
+          <t>298387</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>399952</t>
+          <t>400122</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702411</t>
+          <t>703551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713549</t>
+          <t>714165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12910</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17940</t>
+          <t>18030</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23194</t>
+          <t>23660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>497419</t>
+          <t>497848</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>508628</t>
+          <t>509454</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>571552</t>
+          <t>571462</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>584741</t>
+          <t>585098</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1076628</t>
+          <t>1076162</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1093138</t>
+          <t>1092602</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10926</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>285290</t>
+          <t>285543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>227117</t>
+          <t>227707</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>517769</t>
+          <t>518029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>194204</t>
+          <t>194901</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302358</t>
+          <t>302277</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284305</t>
+          <t>285341</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336636</t>
+          <t>334980</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>626167</t>
+          <t>626168</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>633583</t>
+          <t>633577</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205390</t>
+          <t>205651</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>327426</t>
+          <t>328216</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>536940</t>
+          <t>537518</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28173</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,47 +3184,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>28781</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>18714</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>41885</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>28781</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>18664</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>41428</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1890151</t>
+          <t>1889452</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1904747</t>
+          <t>1904168</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2273189</t>
+          <t>2271553</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2291168</t>
+          <t>2290714</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4170160</t>
+          <t>4169703</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4192924</t>
+          <t>4192874</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312884</t>
+          <t>312840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>319596</t>
+          <t>319612</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>413292</t>
+          <t>410734</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729271</t>
+          <t>730067</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743409</t>
+          <t>743423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>16507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>16633</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26734</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>552969</t>
+          <t>553048</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>566751</t>
+          <t>566768</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>593980</t>
+          <t>593132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>606747</t>
+          <t>606047</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1152587</t>
+          <t>1152495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1170861</t>
+          <t>1170980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>14025</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366745</t>
+          <t>366631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>374207</t>
+          <t>374215</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296915</t>
+          <t>296990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>306620</t>
+          <t>306641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667903</t>
+          <t>668865</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>679739</t>
+          <t>679742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13798</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>13905</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208320</t>
+          <t>208885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>220038</t>
+          <t>219103</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>349594</t>
+          <t>349977</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>360902</t>
+          <t>361339</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>969</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>298823</t>
+          <t>299587</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>344286</t>
+          <t>345016</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>647663</t>
+          <t>647014</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>654921</t>
+          <t>654928</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242089</t>
+          <t>241836</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>373694</t>
+          <t>374483</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>383614</t>
+          <t>383645</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>620241</t>
+          <t>620434</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>631349</t>
+          <t>630514</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28419</t>
+          <t>27855</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18056</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41584</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31692</t>
+          <t>32674</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61375</t>
+          <t>62658</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2108907</t>
+          <t>2109471</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2127599</t>
+          <t>2127848</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2475246</t>
+          <t>2473771</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2498774</t>
+          <t>2497186</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4592781</t>
+          <t>4591498</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4622464</t>
+          <t>4621482</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>5097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>255371</t>
+          <t>255584</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>614007</t>
+          <t>613993</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11508</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17596</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>24742</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452868</t>
+          <t>452238</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>463314</t>
+          <t>463306</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>524326</t>
+          <t>523613</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537289</t>
+          <t>536741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>981984</t>
+          <t>980842</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>998488</t>
+          <t>998212</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9756</t>
+          <t>9640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20177</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325833</t>
+          <t>325143</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336861</t>
+          <t>336784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>306100</t>
+          <t>306216</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>314770</t>
+          <t>314780</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>635637</t>
+          <t>635753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>649538</t>
+          <t>649674</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6704</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123530</t>
+          <t>123558</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199530</t>
+          <t>199752</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>325723</t>
+          <t>326237</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>333857</t>
+          <t>333849</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>295802</t>
+          <t>295137</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>335818</t>
+          <t>335784</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>345116</t>
+          <t>345123</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>635460</t>
+          <t>635367</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>644858</t>
+          <t>644860</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>240056</t>
+          <t>240765</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>382333</t>
+          <t>382014</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>392577</t>
+          <t>392569</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>627290</t>
+          <t>627620</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>638086</t>
+          <t>638546</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27175</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33490</t>
+          <t>33957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28035</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54523</t>
+          <t>56166</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1869753</t>
+          <t>1868839</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1886093</t>
+          <t>1886447</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2301530</t>
+          <t>2301063</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2320099</t>
+          <t>2320272</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4177425</t>
+          <t>4175782</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4203913</t>
+          <t>4202784</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12519</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15512</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21245</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>19245</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,27 +9813,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30649</t>
+          <t>42656</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>37637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>44132</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>51894</t>
+          <t>70101</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42305</t>
+          <t>60787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56235</t>
+          <t>74529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>44132</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>44132</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>44132</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>57817</t>
+          <t>75935</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57817</t>
+          <t>75935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57817</t>
+          <t>75935</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>20665</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>17933</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49353</t>
+          <t>63110</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38806</t>
+          <t>46320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52631</t>
+          <t>66985</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,27 +10156,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>95446</t>
+          <t>110143</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>94757</t>
+          <t>103958</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95608</t>
+          <t>111581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10191,27 +10191,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>144799</t>
+          <t>173254</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134594</t>
+          <t>160634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148239</t>
+          <t>178567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52631</t>
+          <t>66985</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52631</t>
+          <t>66985</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52631</t>
+          <t>66985</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95608</t>
+          <t>111581</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95608</t>
+          <t>111581</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95608</t>
+          <t>111581</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>148239</t>
+          <t>178567</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>148239</t>
+          <t>178567</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>148239</t>
+          <t>178567</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -10361,12 +10361,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -10396,12 +10396,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -10464,27 +10464,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>114974</t>
+          <t>136229</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>109960</t>
+          <t>131220</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117241</t>
+          <t>138200</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10499,27 +10499,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>133528</t>
+          <t>154899</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129752</t>
+          <t>151023</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135038</t>
+          <t>156459</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>248502</t>
+          <t>291129</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242838</t>
+          <t>285803</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251302</t>
+          <t>293609</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>117241</t>
+          <t>138200</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>117241</t>
+          <t>138200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117241</t>
+          <t>138200</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135038</t>
+          <t>156459</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135038</t>
+          <t>156459</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135038</t>
+          <t>156459</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>252279</t>
+          <t>294659</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>252279</t>
+          <t>294659</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>252279</t>
+          <t>294659</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>18435</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13921</t>
+          <t>14988</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11567</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27542</t>
+          <t>29589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>93251</t>
+          <t>107515</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85214</t>
+          <t>99803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98577</t>
+          <t>113186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>102780</t>
+          <t>117744</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97352</t>
+          <t>112446</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106562</t>
+          <t>121838</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>196031</t>
+          <t>225260</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>187322</t>
+          <t>216083</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>203297</t>
+          <t>232267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>103591</t>
+          <t>118238</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>103591</t>
+          <t>118238</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>103591</t>
+          <t>118238</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>127434</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>127434</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>127434</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>214864</t>
+          <t>245672</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>214864</t>
+          <t>245672</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>214864</t>
+          <t>245672</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11727</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>13144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26764</t>
+          <t>28619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52088</t>
+          <t>56993</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45489</t>
+          <t>49447</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56914</t>
+          <t>62027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>62322</t>
+          <t>70432</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57537</t>
+          <t>65523</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65753</t>
+          <t>73942</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>114410</t>
+          <t>127424</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106485</t>
+          <t>118311</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120870</t>
+          <t>133786</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>63815</t>
+          <t>68899</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63815</t>
+          <t>68899</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63815</t>
+          <t>68899</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>69434</t>
+          <t>78031</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69434</t>
+          <t>78031</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69434</t>
+          <t>78031</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>133249</t>
+          <t>146930</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>133249</t>
+          <t>146930</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133249</t>
+          <t>146930</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15398</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71579</t>
+          <t>23308</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>24777</t>
+          <t>27809</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>20787</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79921</t>
+          <t>34910</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>33017</t>
+          <t>35830</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28267</t>
+          <t>30976</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36429</t>
+          <t>39876</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>253975</t>
+          <t>55183</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>197794</t>
+          <t>49252</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>265829</t>
+          <t>60243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>286992</t>
+          <t>91014</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>231848</t>
+          <t>83913</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>305804</t>
+          <t>98036</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>82,51%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42396</t>
+          <t>46262</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42396</t>
+          <t>46262</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42396</t>
+          <t>46262</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>269373</t>
+          <t>72560</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>269373</t>
+          <t>72560</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>269373</t>
+          <t>72560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>311769</t>
+          <t>118823</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>311769</t>
+          <t>118823</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>311769</t>
+          <t>118823</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>39966</t>
+          <t>41562</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32766</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46789</t>
+          <t>49093</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>86062</t>
+          <t>92429</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76361</t>
+          <t>80789</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>95339</t>
+          <t>101831</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>126028</t>
+          <t>133990</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>113274</t>
+          <t>120837</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137770</t>
+          <t>146696</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,6%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>43990</t>
+          <t>48874</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37167</t>
+          <t>41343</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51190</t>
+          <t>56289</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>97853</t>
+          <t>107061</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>88576</t>
+          <t>97659</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107554</t>
+          <t>118701</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>141842</t>
+          <t>155936</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>130100</t>
+          <t>143230</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>154596</t>
+          <t>169089</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,32%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>83956</t>
+          <t>90436</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83956</t>
+          <t>90436</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83956</t>
+          <t>90436</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>183915</t>
+          <t>199490</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>183915</t>
+          <t>199490</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>183915</t>
+          <t>199490</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>267870</t>
+          <t>289926</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>267870</t>
+          <t>289926</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>267870</t>
+          <t>289926</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>81334</t>
+          <t>84828</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66767</t>
+          <t>70340</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99445</t>
+          <t>105299</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>120283</t>
+          <t>131567</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64709</t>
+          <t>115664</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>162854</t>
+          <t>147593</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>201617</t>
+          <t>216395</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118878</t>
+          <t>194694</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>245815</t>
+          <t>241368</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>407919</t>
+          <t>475996</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>389808</t>
+          <t>455525</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>422486</t>
+          <t>490484</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>776551</t>
+          <t>658120</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>733980</t>
+          <t>642094</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>832125</t>
+          <t>674023</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1184470</t>
+          <t>1134116</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1140272</t>
+          <t>1109143</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1267209</t>
+          <t>1155817</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>489253</t>
+          <t>560824</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>489253</t>
+          <t>560824</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>489253</t>
+          <t>560824</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>896834</t>
+          <t>789687</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>896834</t>
+          <t>789687</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>896834</t>
+          <t>789687</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1386087</t>
+          <t>1350511</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1386087</t>
+          <t>1350511</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1386087</t>
+          <t>1350511</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
